--- a/AAII_Financials/Yearly/SSBK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSBK_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/SSBK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSBK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
   <si>
     <t>SSBK</t>
   </si>
@@ -656,82 +656,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>132300</v>
+      </c>
+      <c r="E8" s="3">
         <v>82900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>57800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>50300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>47000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>37200</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -741,9 +744,12 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -774,9 +780,12 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -807,9 +816,12 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,8 +835,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -855,9 +868,12 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,9 +904,12 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -921,9 +940,12 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -954,9 +976,12 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,29 +992,30 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E17" s="3">
         <v>17100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9700</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
@@ -999,30 +1025,33 @@
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E18" s="3">
         <v>65700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>49900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>38300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>29100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>27500</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1032,9 +1061,12 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,29 +1080,30 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-30900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-25600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-23600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-21100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-17500</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1080,30 +1113,33 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E21" s="3">
         <v>36300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>26500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>16900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11200</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1113,9 +1149,12 @@
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1146,75 +1185,84 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E23" s="3">
         <v>34800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>24300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>14600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>10000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9100</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E24" s="3">
         <v>7700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5700</v>
-      </c>
-      <c r="F24" s="3">
-        <v>2500</v>
       </c>
       <c r="G24" s="3">
         <v>2500</v>
       </c>
       <c r="H24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I24" s="3">
         <v>2300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3200</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,30 +1293,33 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E26" s="3">
         <v>27100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>18600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7700</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1278,30 +1329,33 @@
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E27" s="3">
         <v>27100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>18600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7700</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1311,9 +1365,12 @@
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,9 +1401,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1377,9 +1437,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1473,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,30 +1509,33 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E32" s="3">
         <v>30900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>25600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>23600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>21100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>17500</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1476,30 +1545,33 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E33" s="3">
         <v>27100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>18600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7700</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1509,9 +1581,12 @@
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,30 +1617,33 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E35" s="3">
         <v>27100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>18600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7700</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1575,47 +1653,53 @@
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1713,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,62 +1729,66 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E41" s="3">
         <v>15300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>23200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>68500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>41600</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>230900</v>
+      </c>
+      <c r="E42" s="3">
         <v>153200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>277600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>61700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>101700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>79400</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1709,9 +1798,12 @@
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1742,9 +1834,12 @@
       <c r="L43" s="3">
         <v>0</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1775,9 +1870,12 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1808,9 +1906,12 @@
       <c r="L45" s="3">
         <v>0</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -1841,26 +1942,29 @@
       <c r="L46" s="3">
         <v>0</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E47" s="3">
         <v>4400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5000</v>
       </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
+      <c r="H47" s="3">
+        <v>0</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -1874,30 +1978,33 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E48" s="3">
         <v>27300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>27000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>16300</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1907,42 +2014,48 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E49" s="3">
         <v>18100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6600</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2086,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,9 +2122,12 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2039,9 +2158,12 @@
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,42 +2194,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2446700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2045200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1782600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1332500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1095500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>887600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>735500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>628600</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2249,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,29 +2265,30 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>300</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2168,9 +2298,12 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2201,9 +2334,12 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2234,9 +2370,12 @@
       <c r="L59" s="3">
         <v>0</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2267,20 +2406,23 @@
       <c r="L60" s="3">
         <v>0</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3">
+        <v>0</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>86700</v>
+      </c>
+      <c r="E61" s="3">
         <v>86300</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
         <v>4500</v>
@@ -2289,7 +2431,7 @@
         <v>4500</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2300,9 +2442,12 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2333,9 +2478,12 @@
       <c r="L62" s="3">
         <v>0</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2514,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2550,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,42 +2586,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2231700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1863500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1605400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1191800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>968900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>792100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>645700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>546500</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2641,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2674,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2710,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2579,9 +2746,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,30 +2782,33 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>102500</v>
+      </c>
+      <c r="E72" s="3">
         <v>73800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>49900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>34200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>23900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>20700</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,9 +2818,12 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2854,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2890,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,42 +2926,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E76" s="3">
         <v>181700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>177200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>140700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>126600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>95500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>89800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>82000</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,68 +2998,74 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E81" s="3">
         <v>27100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>18600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7700</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
@@ -2881,9 +3075,12 @@
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,8 +3094,9 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2906,20 +3104,20 @@
         <v>1500</v>
       </c>
       <c r="E83" s="3">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="F83" s="3">
         <v>2200</v>
       </c>
       <c r="G83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H83" s="3">
         <v>1300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1200</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
@@ -2929,9 +3127,12 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3163,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3199,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3235,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3271,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,30 +3307,33 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E89" s="3">
         <v>38900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>29700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>12100</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3127,9 +3343,12 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,29 +3362,30 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,9 +3395,12 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3431,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,30 +3467,33 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-318800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-387200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-260800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-260100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>36400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-137600</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3274,9 +3503,12 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,8 +3522,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3299,11 +3532,11 @@
         <v>-3200</v>
       </c>
       <c r="E96" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F96" s="3">
         <v>-2900</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
@@ -3322,9 +3555,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3591,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3627,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,30 +3663,33 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>361600</v>
+      </c>
+      <c r="E100" s="3">
         <v>232800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>430100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>218300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-18600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>143400</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3454,9 +3699,12 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3481,36 +3729,39 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>82200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-115500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>199000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-30300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>28800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>17900</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3520,7 +3771,10 @@
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SSBK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSBK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
   <si>
     <t>SSBK</t>
   </si>
@@ -662,7 +662,9 @@
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -699,8 +701,8 @@
       <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
-        <v>43100</v>
+      <c r="J7" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K7" s="2">
         <v>42735</v>
@@ -718,22 +720,22 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>132300</v>
+        <v>82900</v>
       </c>
       <c r="E8" s="3">
-        <v>82900</v>
+        <v>74400</v>
       </c>
       <c r="F8" s="3">
-        <v>57800</v>
+        <v>60700</v>
       </c>
       <c r="G8" s="3">
-        <v>50300</v>
+        <v>46800</v>
       </c>
       <c r="H8" s="3">
-        <v>47000</v>
+        <v>35900</v>
       </c>
       <c r="I8" s="3">
-        <v>37200</v>
+        <v>30900</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -789,23 +791,23 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>82900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>74400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>60700</v>
+      </c>
+      <c r="G10" s="3">
+        <v>46800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>35900</v>
+      </c>
+      <c r="I10" s="3">
+        <v>30900</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -913,26 +915,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>3400</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -950,22 +952,22 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -999,22 +1001,22 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>58200</v>
+        <v>40700</v>
       </c>
       <c r="E17" s="3">
-        <v>17100</v>
+        <v>38700</v>
       </c>
       <c r="F17" s="3">
-        <v>7800</v>
+        <v>35500</v>
       </c>
       <c r="G17" s="3">
-        <v>12000</v>
+        <v>31400</v>
       </c>
       <c r="H17" s="3">
-        <v>17800</v>
+        <v>24200</v>
       </c>
       <c r="I17" s="3">
-        <v>9700</v>
+        <v>20900</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
@@ -1035,22 +1037,22 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>74000</v>
+        <v>42200</v>
       </c>
       <c r="E18" s="3">
-        <v>65700</v>
+        <v>35700</v>
       </c>
       <c r="F18" s="3">
-        <v>49900</v>
+        <v>25300</v>
       </c>
       <c r="G18" s="3">
-        <v>38300</v>
+        <v>15400</v>
       </c>
       <c r="H18" s="3">
-        <v>29100</v>
+        <v>11700</v>
       </c>
       <c r="I18" s="3">
-        <v>27500</v>
+        <v>10000</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
@@ -1087,22 +1089,22 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-33000</v>
+        <v>1200</v>
       </c>
       <c r="E20" s="3">
-        <v>-30900</v>
+        <v>900</v>
       </c>
       <c r="F20" s="3">
-        <v>-25600</v>
+        <v>1000</v>
       </c>
       <c r="G20" s="3">
-        <v>-23600</v>
+        <v>800</v>
       </c>
       <c r="H20" s="3">
-        <v>-21100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-17500</v>
+        <v>200</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1135,13 +1137,13 @@
         <v>16900</v>
       </c>
       <c r="H21" s="3">
-        <v>9400</v>
+        <v>12800</v>
       </c>
       <c r="I21" s="3">
         <v>11200</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+      <c r="J21" s="3">
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1158,26 +1160,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1212,8 +1214,8 @@
       <c r="I23" s="3">
         <v>10000</v>
       </c>
-      <c r="J23" s="3">
-        <v>9400</v>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K23" s="3">
         <v>9100</v>
@@ -1248,8 +1250,8 @@
       <c r="I24" s="3">
         <v>2300</v>
       </c>
-      <c r="J24" s="3">
-        <v>3800</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>3200</v>
@@ -1339,7 +1341,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>32000</v>
+        <v>31900</v>
       </c>
       <c r="E27" s="3">
         <v>27100</v>
@@ -1519,22 +1521,22 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>33000</v>
+        <v>-1200</v>
       </c>
       <c r="E32" s="3">
-        <v>30900</v>
+        <v>-900</v>
       </c>
       <c r="F32" s="3">
-        <v>25600</v>
+        <v>-1000</v>
       </c>
       <c r="G32" s="3">
-        <v>23600</v>
+        <v>-800</v>
       </c>
       <c r="H32" s="3">
-        <v>21100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>17500</v>
+        <v>-200</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1685,8 +1687,8 @@
       <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
-        <v>43100</v>
+      <c r="J38" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K38" s="2">
         <v>42735</v>
@@ -1736,25 +1738,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>19700</v>
+        <v>250700</v>
       </c>
       <c r="E41" s="3">
-        <v>15300</v>
+        <v>168500</v>
       </c>
       <c r="F41" s="3">
-        <v>6400</v>
+        <v>284000</v>
       </c>
       <c r="G41" s="3">
-        <v>23200</v>
+        <v>84900</v>
       </c>
       <c r="H41" s="3">
-        <v>13500</v>
+        <v>115200</v>
       </c>
       <c r="I41" s="3">
-        <v>7000</v>
-      </c>
-      <c r="J41" s="3">
-        <v>68500</v>
+        <v>85000</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K41" s="3">
         <v>41600</v>
@@ -1772,25 +1774,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>230900</v>
+        <v>7700</v>
       </c>
       <c r="E42" s="3">
-        <v>153200</v>
+        <v>8900</v>
       </c>
       <c r="F42" s="3">
-        <v>277600</v>
+        <v>1800</v>
       </c>
       <c r="G42" s="3">
-        <v>61700</v>
+        <v>1000</v>
       </c>
       <c r="H42" s="3">
-        <v>101700</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>79400</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1807,26 +1809,26 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -1847,22 +1849,22 @@
         <v>0</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+        <v>600</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1880,25 +1882,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+        <v>2600</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -1916,25 +1918,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>267500</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>188300</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>295200</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>106100</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>127800</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3">
-        <v>0</v>
+        <v>89900</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -1952,22 +1954,22 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3600</v>
+        <v>207000</v>
       </c>
       <c r="E47" s="3">
-        <v>4400</v>
+        <v>181800</v>
       </c>
       <c r="F47" s="3">
-        <v>9200</v>
+        <v>162800</v>
       </c>
       <c r="G47" s="3">
-        <v>5000</v>
+        <v>121300</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
+        <v>61000</v>
+      </c>
+      <c r="I47" s="3">
+        <v>53100</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
@@ -2041,8 +2043,8 @@
       <c r="I49" s="3">
         <v>6400</v>
       </c>
-      <c r="J49" s="3">
-        <v>6500</v>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3">
         <v>6600</v>
@@ -2132,25 +2134,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>54400</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>51200</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>39700</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>41100</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>37300</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+        <v>24500</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2221,8 +2223,8 @@
       <c r="I54" s="3">
         <v>887600</v>
       </c>
-      <c r="J54" s="3">
-        <v>735500</v>
+      <c r="J54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K54" s="3">
         <v>628600</v>
@@ -2272,22 +2274,22 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1500</v>
+        <v>2018200</v>
       </c>
       <c r="E57" s="3">
-        <v>600</v>
+        <v>1720700</v>
       </c>
       <c r="F57" s="3">
-        <v>100</v>
+        <v>1556500</v>
       </c>
       <c r="G57" s="3">
-        <v>300</v>
+        <v>1139700</v>
       </c>
       <c r="H57" s="3">
-        <v>500</v>
+        <v>950500</v>
       </c>
       <c r="I57" s="3">
-        <v>300</v>
+        <v>775800</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
@@ -2308,25 +2310,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>104900</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>39900</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>40300</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>39900</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+        <v>7500</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2343,26 +2345,26 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -2380,25 +2382,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>2124600</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1761200</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>1596900</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>1179800</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>959000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3">
-        <v>0</v>
+        <v>783600</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2416,7 +2418,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>86700</v>
+        <v>87000</v>
       </c>
       <c r="E61" s="3">
         <v>86300</v>
@@ -2452,25 +2454,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>11600</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+        <v>2200</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -2605,7 +2607,7 @@
         <v>1605400</v>
       </c>
       <c r="G66" s="3">
-        <v>1191800</v>
+        <v>1191900</v>
       </c>
       <c r="H66" s="3">
         <v>968900</v>
@@ -2613,8 +2615,8 @@
       <c r="I66" s="3">
         <v>792100</v>
       </c>
-      <c r="J66" s="3">
-        <v>645700</v>
+      <c r="J66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K66" s="3">
         <v>546500</v>
@@ -2953,8 +2955,8 @@
       <c r="I76" s="3">
         <v>95500</v>
       </c>
-      <c r="J76" s="3">
-        <v>89800</v>
+      <c r="J76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K76" s="3">
         <v>82000</v>
@@ -3030,8 +3032,8 @@
       <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
-        <v>43100</v>
+      <c r="J80" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K80" s="2">
         <v>42735</v>
@@ -3101,22 +3103,22 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="E83" s="3">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="F83" s="3">
-        <v>2200</v>
+        <v>1900</v>
       </c>
       <c r="G83" s="3">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="H83" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="I83" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -3529,22 +3531,22 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3200</v>
+        <v>3200</v>
       </c>
       <c r="E96" s="3">
-        <v>-3200</v>
+        <v>3200</v>
       </c>
       <c r="F96" s="3">
-        <v>-2900</v>
+        <v>2900</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -3708,26 +3710,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -3762,8 +3764,8 @@
       <c r="I102" s="3">
         <v>17900</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/SSBK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SSBK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
   <si>
     <t>SSBK</t>
   </si>
@@ -656,90 +656,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="K7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>94100</v>
+      </c>
+      <c r="E8" s="3">
         <v>82900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>74400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>60700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>46800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>35900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>30900</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
@@ -749,9 +752,12 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -785,33 +791,36 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>94100</v>
+      </c>
+      <c r="E10" s="3">
         <v>82900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>74400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>60700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>46800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>35900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>30900</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
@@ -821,9 +830,12 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -838,8 +850,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -873,9 +886,12 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -909,17 +925,20 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1600</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -927,17 +946,17 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>3400</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -945,33 +964,36 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="E15" s="3">
         <v>1500</v>
       </c>
       <c r="F15" s="3">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="G15" s="3">
         <v>2200</v>
       </c>
       <c r="H15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I15" s="3">
         <v>1300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1200</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
@@ -981,9 +1003,12 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -995,32 +1020,33 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>40700</v>
+        <v>45400</v>
       </c>
       <c r="E17" s="3">
+        <v>39100</v>
+      </c>
+      <c r="F17" s="3">
         <v>38700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>31400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>24200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20900</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1030,33 +1056,36 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>42200</v>
+        <v>48700</v>
       </c>
       <c r="E18" s="3">
+        <v>43800</v>
+      </c>
+      <c r="F18" s="3">
         <v>35700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>25300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>15400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>11700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10000</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1066,9 +1095,12 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1083,29 +1115,30 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E20" s="3">
         <v>1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1118,35 +1151,38 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>42500</v>
+        <v>49200</v>
       </c>
       <c r="E21" s="3">
+        <v>44100</v>
+      </c>
+      <c r="F21" s="3">
         <v>36300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>26500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>16900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>12800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11200</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
+      <c r="K21" s="3">
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
@@ -1154,9 +1190,12 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1181,8 +1220,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1190,81 +1229,90 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E23" s="3">
         <v>41000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>34800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>24300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>14600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10000</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="3">
         <v>9100</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E24" s="3">
         <v>9100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5700</v>
-      </c>
-      <c r="G24" s="3">
-        <v>2500</v>
       </c>
       <c r="H24" s="3">
         <v>2500</v>
       </c>
       <c r="I24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J24" s="3">
         <v>2300</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
         <v>3200</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1298,33 +1346,36 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E26" s="3">
         <v>32000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>27100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>18600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7700</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1334,33 +1385,36 @@
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E27" s="3">
         <v>31900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>27100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>18600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>12100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7700</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1370,9 +1424,12 @@
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1406,9 +1463,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1442,9 +1502,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1478,9 +1541,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1514,30 +1580,33 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1550,33 +1619,36 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E33" s="3">
         <v>32000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>27100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>18600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>12100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7700</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1586,9 +1658,12 @@
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1622,33 +1697,36 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E35" s="3">
         <v>32000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>27100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>18600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>12100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7700</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1658,50 +1736,56 @@
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K38" s="2">
+      <c r="K38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1716,8 +1800,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1732,70 +1817,74 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>260200</v>
+      </c>
+      <c r="E41" s="3">
         <v>250700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>168500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>284000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>84900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>115200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>85000</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3">
         <v>41600</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E42" s="3">
         <v>7700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1000</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
@@ -1803,9 +1892,12 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1824,14 +1916,14 @@
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -1839,35 +1931,38 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E44" s="3">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="F44" s="3">
         <v>2900</v>
       </c>
       <c r="G44" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H44" s="3">
         <v>10200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>600</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -1875,35 +1970,38 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E45" s="3">
         <v>8700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>4200</v>
       </c>
       <c r="G45" s="3">
         <v>4200</v>
       </c>
       <c r="H45" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I45" s="3">
         <v>3000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2600</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -1911,35 +2009,38 @@
       <c r="M45" s="3">
         <v>0</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>277200</v>
+      </c>
+      <c r="E46" s="3">
         <v>267500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>188300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>295200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>106100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>127800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>89900</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3">
-        <v>0</v>
+      <c r="K46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L46" s="3">
         <v>0</v>
@@ -1947,33 +2048,36 @@
       <c r="M46" s="3">
         <v>0</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3">
+        <v>0</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>223200</v>
+      </c>
+      <c r="E47" s="3">
         <v>207000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>181800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>162800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>121300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>61000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>53100</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1983,33 +2087,36 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>26400</v>
+        <v>33000</v>
       </c>
       <c r="E48" s="3">
+        <v>27000</v>
+      </c>
+      <c r="F48" s="3">
         <v>27300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>27000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>24400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>16300</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2019,45 +2126,51 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>42100</v>
+      </c>
+      <c r="E49" s="3">
         <v>17800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6400</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K49" s="3">
+      <c r="K49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L49" s="3">
         <v>6600</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2091,9 +2204,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2127,35 +2243,38 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>54400</v>
+        <v>62700</v>
       </c>
       <c r="E52" s="3">
+        <v>53800</v>
+      </c>
+      <c r="F52" s="3">
         <v>51200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>39700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>41100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>37300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>24500</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -2163,9 +2282,12 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2199,45 +2321,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2848300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2446700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2045200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1782600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1332500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1095500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>887600</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3">
         <v>628600</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2252,8 +2380,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2268,32 +2397,33 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2411300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2018200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1720700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1556500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1139700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>950500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>775800</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2303,35 +2433,38 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>104900</v>
+        <v>46700</v>
       </c>
       <c r="E58" s="3">
+        <v>104700</v>
+      </c>
+      <c r="F58" s="3">
         <v>39900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>40300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>39900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7500</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -2339,9 +2472,12 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2366,8 +2502,8 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -2375,35 +2511,38 @@
       <c r="M59" s="3">
         <v>0</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2124600</v>
+        <v>2460200</v>
       </c>
       <c r="E60" s="3">
+        <v>2124400</v>
+      </c>
+      <c r="F60" s="3">
         <v>1761200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1596900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1179800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>959000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>783600</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3">
-        <v>0</v>
+      <c r="K60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L60" s="3">
         <v>0</v>
@@ -2411,23 +2550,26 @@
       <c r="M60" s="3">
         <v>0</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3">
+        <v>0</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>87000</v>
+        <v>91900</v>
       </c>
       <c r="E61" s="3">
+        <v>87200</v>
+      </c>
+      <c r="F61" s="3">
         <v>86300</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>4500</v>
@@ -2436,7 +2578,7 @@
         <v>4500</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2447,35 +2589,38 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E62" s="3">
         <v>15000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>11600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2200</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -2483,9 +2628,12 @@
       <c r="M62" s="3">
         <v>0</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2519,9 +2667,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2555,9 +2706,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2591,45 +2745,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2568400</v>
+      </c>
+      <c r="E66" s="3">
         <v>2231700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1863500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1605400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1191900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>968900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>792100</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3">
         <v>546500</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2644,8 +2804,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2679,9 +2840,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2715,9 +2879,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2751,9 +2918,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2787,33 +2957,36 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>134100</v>
+      </c>
+      <c r="E72" s="3">
         <v>102500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>73800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>49900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>34200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>23900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>20700</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2823,9 +2996,12 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2859,9 +3035,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2895,9 +3074,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2931,45 +3113,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>279900</v>
+      </c>
+      <c r="E76" s="3">
         <v>215000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>181700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>177200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>140700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>126600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>95500</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3">
         <v>82000</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3003,74 +3191,80 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K80" s="2">
+      <c r="K80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E81" s="3">
         <v>32000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>27100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>18600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>12100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7700</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3080,9 +3274,12 @@
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3097,31 +3294,32 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E83" s="3">
         <v>1200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1100</v>
       </c>
       <c r="I83" s="3">
         <v>1100</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="J83" s="3">
+        <v>1100</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3132,9 +3330,12 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3168,9 +3369,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3204,9 +3408,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3240,9 +3447,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3276,9 +3486,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3312,33 +3525,36 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E89" s="3">
         <v>39400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>38900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>29700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>12100</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3348,9 +3564,12 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3365,32 +3584,33 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3400,9 +3620,12 @@
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3436,9 +3659,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3472,33 +3698,36 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-54900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-318800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-387200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-260800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-260100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>36400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-137600</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3508,9 +3737,12 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3525,32 +3757,33 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="E96" s="3">
         <v>3200</v>
       </c>
       <c r="F96" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G96" s="3">
         <v>2900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1900</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
@@ -3560,9 +3793,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3596,9 +3832,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3632,9 +3871,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3668,33 +3910,36 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E100" s="3">
         <v>361600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>232800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>430100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>218300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-18600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>143400</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3704,9 +3949,12 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3731,44 +3979,47 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E102" s="3">
         <v>82200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-115500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>199000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-30300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>28800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>17900</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
@@ -3776,7 +4027,10 @@
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
